--- a/pruebas-crudas/12-prueba-guiada.xlsx
+++ b/pruebas-crudas/12-prueba-guiada.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -608,30 +608,53 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>PF-201</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Pastilla freno delantera</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Bosch</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Frenos</v>
+      </c>
+      <c r="E10">
+        <v>24990</v>
+      </c>
+      <c r="F10">
+        <v>12</v>
+      </c>
+      <c r="G10" t="str">
+        <v>NISSAN V16 1995-2008</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v/>
       </c>
-      <c r="B10" t="str">
+      <c r="B11" t="str">
         <v>SUBTOTAL</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C11" t="str">
         <v/>
       </c>
-      <c r="D10" t="str">
+      <c r="D11" t="str">
         <v/>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>237930</v>
       </c>
-      <c r="F10">
+      <c r="F11">
         <v>68</v>
       </c>
-      <c r="G10" t="str">
+      <c r="G11" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
   </ignoredErrors>
 </worksheet>
 </file>